--- a/BOSTON/massachusetts_citycrime.xlsx
+++ b/BOSTON/massachusetts_citycrime.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43A5886A-0EB4-234F-8AFB-6359E341AEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E6E91B-8B4E-9540-96EC-3B4D3E465D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{ABB194F8-BE1B-0B46-A88A-BC8720696E80}"/>
   </bookViews>
@@ -15,18 +15,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'19tbl08ma'!$1:$1</definedName>
     <definedName name="Tables_8_11_2015_31_UCR02200" localSheetId="0">'19tbl08ma'!$A$2:$I$282</definedName>
   </definedNames>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -67,10 +56,6 @@
     <t>Burglary</t>
   </si>
   <si>
-    <t>Larceny-
-theft</t>
-  </si>
-  <si>
     <t>Ashland</t>
   </si>
   <si>
@@ -951,6 +936,9 @@
   </si>
   <si>
     <t>Violent_crime</t>
+  </si>
+  <si>
+    <t>Larceny_theft</t>
   </si>
 </sst>
 </file>
@@ -1879,52 +1867,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D964CB9-D3B1-C546-949E-168E81A49232}">
   <dimension ref="A1:I282"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="27" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="2"/>
+    <col min="1" max="1" width="27" style="2"/>
+    <col min="2" max="9" width="27" style="9"/>
+    <col min="10" max="16384" width="27" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="50.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="8">
         <v>16448</v>
@@ -1953,7 +1934,7 @@
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" s="8">
         <v>23780</v>
@@ -1982,7 +1963,7 @@
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="8">
         <v>10533</v>
@@ -2011,7 +1992,7 @@
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="8">
         <v>8028</v>
@@ -2040,7 +2021,7 @@
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="8">
         <v>28736</v>
@@ -2069,7 +2050,7 @@
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="8">
         <v>17595</v>
@@ -2098,7 +2079,7 @@
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" s="8">
         <v>39603</v>
@@ -2127,7 +2108,7 @@
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="8">
         <v>36547</v>
@@ -2156,7 +2137,7 @@
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B10" s="8">
         <v>328</v>
@@ -2185,7 +2166,7 @@
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="8">
         <v>45614</v>
@@ -2214,7 +2195,7 @@
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="8">
         <v>6330</v>
@@ -2243,7 +2224,7 @@
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="8">
         <v>17742</v>
@@ -2272,7 +2253,7 @@
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B14" s="8">
         <v>11679</v>
@@ -2301,7 +2282,7 @@
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15" s="8">
         <v>44959</v>
@@ -2330,7 +2311,7 @@
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="8">
         <v>16724</v>
@@ -2359,7 +2340,7 @@
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" ht="18.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B17" s="8">
         <v>4504</v>
@@ -2388,7 +2369,7 @@
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18" s="8">
         <v>8192</v>
@@ -2417,7 +2398,7 @@
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="8">
         <v>44032</v>
@@ -2446,7 +2427,7 @@
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B20" s="8">
         <v>5573</v>
@@ -2475,7 +2456,7 @@
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" ht="18.75" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B21" s="8">
         <v>1724</v>
@@ -2504,7 +2485,7 @@
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="8">
         <v>14193</v>
@@ -2533,7 +2514,7 @@
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>15195</v>
@@ -2562,7 +2543,7 @@
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="8">
         <v>17143</v>
@@ -2591,7 +2572,7 @@
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="8">
         <v>26331</v>
@@ -2620,7 +2601,7 @@
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B26" s="8">
         <v>6799</v>
@@ -2649,7 +2630,7 @@
     </row>
     <row r="27" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="8">
         <v>3241</v>
@@ -2678,7 +2659,7 @@
     </row>
     <row r="28" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B28" s="8">
         <v>2113</v>
@@ -2707,7 +2688,7 @@
     </row>
     <row r="29" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B29" s="8">
         <v>42317</v>
@@ -2736,7 +2717,7 @@
     </row>
     <row r="30" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B30" s="8">
         <v>43882</v>
@@ -2765,7 +2746,7 @@
     </row>
     <row r="31" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B31" s="8">
         <v>9294</v>
@@ -2794,7 +2775,7 @@
     </row>
     <row r="32" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B32" s="8">
         <v>5393</v>
@@ -2823,7 +2804,7 @@
     </row>
     <row r="33" spans="1:9" s="3" customFormat="1" ht="18.75" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B33" s="8">
         <v>698941</v>
@@ -2852,7 +2833,7 @@
     </row>
     <row r="34" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="8">
         <v>19734</v>
@@ -2881,7 +2862,7 @@
     </row>
     <row r="35" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" s="8">
         <v>6540</v>
@@ -2910,7 +2891,7 @@
     </row>
     <row r="36" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="8">
         <v>8352</v>
@@ -2939,7 +2920,7 @@
     </row>
     <row r="37" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B37" s="8">
         <v>4694</v>
@@ -2968,7 +2949,7 @@
     </row>
     <row r="38" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B38" s="8">
         <v>37145</v>
@@ -2997,7 +2978,7 @@
     </row>
     <row r="39" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="8">
         <v>9725</v>
@@ -3026,7 +3007,7 @@
     </row>
     <row r="40" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B40" s="8">
         <v>27270</v>
@@ -3055,7 +3036,7 @@
     </row>
     <row r="41" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B41" s="8">
         <v>95287</v>
@@ -3084,7 +3065,7 @@
     </row>
     <row r="42" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B42" s="8">
         <v>3440</v>
@@ -3113,7 +3094,7 @@
     </row>
     <row r="43" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B43" s="8">
         <v>58928</v>
@@ -3142,7 +3123,7 @@
     </row>
     <row r="44" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B44" s="8">
         <v>29082</v>
@@ -3171,7 +3152,7 @@
     </row>
     <row r="45" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="8">
         <v>119908</v>
@@ -3200,7 +3181,7 @@
     </row>
     <row r="46" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B46" s="8">
         <v>23706</v>
@@ -3229,7 +3210,7 @@
     </row>
     <row r="47" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B47" s="8">
         <v>5255</v>
@@ -3258,7 +3239,7 @@
     </row>
     <row r="48" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B48" s="8">
         <v>11721</v>
@@ -3287,7 +3268,7 @@
     </row>
     <row r="49" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B49" s="8">
         <v>13679</v>
@@ -3316,7 +3297,7 @@
     </row>
     <row r="50" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" s="8">
         <v>6117</v>
@@ -3345,7 +3326,7 @@
     </row>
     <row r="51" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B51" s="8">
         <v>35218</v>
@@ -3374,7 +3355,7 @@
     </row>
     <row r="52" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B52" s="8">
         <v>40496</v>
@@ -3403,7 +3384,7 @@
     </row>
     <row r="53" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B53" s="8">
         <v>3133</v>
@@ -3432,7 +3413,7 @@
     </row>
     <row r="54" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B54" s="8">
         <v>55293</v>
@@ -3461,7 +3442,7 @@
     </row>
     <row r="55" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B55" s="8">
         <v>920</v>
@@ -3490,7 +3471,7 @@
     </row>
     <row r="56" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="8">
         <v>13964</v>
@@ -3519,7 +3500,7 @@
     </row>
     <row r="57" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B57" s="8">
         <v>8609</v>
@@ -3548,7 +3529,7 @@
     </row>
     <row r="58" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A58" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="8">
         <v>19253</v>
@@ -3577,7 +3558,7 @@
     </row>
     <row r="59" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" s="8">
         <v>6546</v>
@@ -3606,7 +3587,7 @@
     </row>
     <row r="60" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" s="8">
         <v>27664</v>
@@ -3635,7 +3616,7 @@
     </row>
     <row r="61" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B61" s="8">
         <v>34035</v>
@@ -3664,7 +3645,7 @@
     </row>
     <row r="62" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B62" s="8">
         <v>25203</v>
@@ -3693,7 +3674,7 @@
     </row>
     <row r="63" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="8">
         <v>5032</v>
@@ -3722,7 +3703,7 @@
     </row>
     <row r="64" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A64" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B64" s="8">
         <v>13738</v>
@@ -3751,7 +3732,7 @@
     </row>
     <row r="65" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B65" s="8">
         <v>8946</v>
@@ -3780,7 +3761,7 @@
     </row>
     <row r="66" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B66" s="8">
         <v>6118</v>
@@ -3809,7 +3790,7 @@
     </row>
     <row r="67" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B67" s="8">
         <v>31786</v>
@@ -3838,7 +3819,7 @@
     </row>
     <row r="68" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B68" s="8">
         <v>11754</v>
@@ -3867,7 +3848,7 @@
     </row>
     <row r="69" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B69" s="8">
         <v>3405</v>
@@ -3896,7 +3877,7 @@
     </row>
     <row r="70" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A70" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B70" s="8">
         <v>15934</v>
@@ -3925,7 +3906,7 @@
     </row>
     <row r="71" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B71" s="8">
         <v>14472</v>
@@ -3954,7 +3935,7 @@
     </row>
     <row r="72" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B72" s="8">
         <v>2202</v>
@@ -3983,7 +3964,7 @@
     </row>
     <row r="73" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B73" s="8">
         <v>4823</v>
@@ -4012,7 +3993,7 @@
     </row>
     <row r="74" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A74" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B74" s="8">
         <v>15979</v>
@@ -4041,7 +4022,7 @@
     </row>
     <row r="75" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B75" s="8">
         <v>16269</v>
@@ -4070,7 +4051,7 @@
     </row>
     <row r="76" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A76" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B76" s="8">
         <v>25079</v>
@@ -4099,7 +4080,7 @@
     </row>
     <row r="77" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B77" s="8">
         <v>4362</v>
@@ -4128,7 +4109,7 @@
     </row>
     <row r="78" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B78" s="8">
         <v>1771</v>
@@ -4157,7 +4138,7 @@
     </row>
     <row r="79" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B79" s="8">
         <v>47195</v>
@@ -4186,7 +4167,7 @@
     </row>
     <row r="80" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B80" s="8">
         <v>15996</v>
@@ -4215,7 +4196,7 @@
     </row>
     <row r="81" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B81" s="8">
         <v>89066</v>
@@ -4244,7 +4225,7 @@
     </row>
     <row r="82" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A82" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B82" s="8">
         <v>30717</v>
@@ -4273,7 +4254,7 @@
     </row>
     <row r="83" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B83" s="8">
         <v>40621</v>
@@ -4302,7 +4283,7 @@
     </row>
     <row r="84" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B84" s="8">
         <v>17631</v>
@@ -4331,7 +4312,7 @@
     </row>
     <row r="85" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A85" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B85" s="8">
         <v>73127</v>
@@ -4360,7 +4341,7 @@
     </row>
     <row r="86" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B86" s="8">
         <v>33149</v>
@@ -4389,7 +4370,7 @@
     </row>
     <row r="87" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B87" s="8">
         <v>9388</v>
@@ -4418,7 +4399,7 @@
     </row>
     <row r="88" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B88" s="8">
         <v>20628</v>
@@ -4447,7 +4428,7 @@
     </row>
     <row r="89" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A89" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B89" s="8">
         <v>8777</v>
@@ -4476,7 +4457,7 @@
     </row>
     <row r="90" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A90" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B90" s="8">
         <v>1490</v>
@@ -4505,7 +4486,7 @@
     </row>
     <row r="91" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A91" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B91" s="8">
         <v>30362</v>
@@ -4534,7 +4515,7 @@
     </row>
     <row r="92" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A92" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B92" s="8">
         <v>1065</v>
@@ -4563,7 +4544,7 @@
     </row>
     <row r="93" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A93" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B93" s="8">
         <v>18880</v>
@@ -4592,7 +4573,7 @@
     </row>
     <row r="94" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A94" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B94" s="8">
         <v>6360</v>
@@ -4621,7 +4602,7 @@
     </row>
     <row r="95" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A95" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B95" s="8">
         <v>6822</v>
@@ -4650,7 +4631,7 @@
     </row>
     <row r="96" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A96" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B96" s="8">
         <v>17464</v>
@@ -4679,7 +4660,7 @@
     </row>
     <row r="97" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A97" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B97" s="8">
         <v>11388</v>
@@ -4708,7 +4689,7 @@
     </row>
     <row r="98" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A98" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B98" s="8">
         <v>6846</v>
@@ -4737,7 +4718,7 @@
     </row>
     <row r="99" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A99" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B99" s="8">
         <v>5358</v>
@@ -4766,7 +4747,7 @@
     </row>
     <row r="100" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A100" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B100" s="8">
         <v>7874</v>
@@ -4795,7 +4776,7 @@
     </row>
     <row r="101" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A101" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B101" s="8">
         <v>8075</v>
@@ -4824,7 +4805,7 @@
     </row>
     <row r="102" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A102" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B102" s="8">
         <v>5199</v>
@@ -4853,7 +4834,7 @@
     </row>
     <row r="103" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A103" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B103" s="8">
         <v>14485</v>
@@ -4882,7 +4863,7 @@
     </row>
     <row r="104" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A104" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B104" s="8">
         <v>10876</v>
@@ -4911,7 +4892,7 @@
     </row>
     <row r="105" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A105" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B105" s="8">
         <v>3039</v>
@@ -4940,7 +4921,7 @@
     </row>
     <row r="106" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A106" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B106" s="8">
         <v>6569</v>
@@ -4969,7 +4950,7 @@
     </row>
     <row r="107" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A107" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B107" s="8">
         <v>12028</v>
@@ -4998,7 +4979,7 @@
     </row>
     <row r="108" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A108" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B108" s="8">
         <v>3286</v>
@@ -5027,7 +5008,7 @@
     </row>
     <row r="109" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A109" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B109" s="8">
         <v>63935</v>
@@ -5056,7 +5037,7 @@
     </row>
     <row r="110" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A110" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B110" s="8">
         <v>23960</v>
@@ -5085,7 +5066,7 @@
     </row>
     <row r="111" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A111" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B111" s="8">
         <v>10990</v>
@@ -5114,7 +5095,7 @@
     </row>
     <row r="112" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A112" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B112" s="8">
         <v>2484</v>
@@ -5143,7 +5124,7 @@
     </row>
     <row r="113" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A113" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B113" s="8">
         <v>14996</v>
@@ -5172,7 +5153,7 @@
     </row>
     <row r="114" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A114" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B114" s="8">
         <v>40178</v>
@@ -5201,7 +5182,7 @@
     </row>
     <row r="115" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A115" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B115" s="8">
         <v>5929</v>
@@ -5230,7 +5211,7 @@
     </row>
     <row r="116" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A116" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B116" s="8">
         <v>18585</v>
@@ -5259,7 +5240,7 @@
     </row>
     <row r="117" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A117" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B117" s="8">
         <v>10402</v>
@@ -5288,7 +5269,7 @@
     </row>
     <row r="118" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A118" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B118" s="8">
         <v>14095</v>
@@ -5317,7 +5298,7 @@
     </row>
     <row r="119" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A119" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B119" s="8">
         <v>13758</v>
@@ -5346,7 +5327,7 @@
     </row>
     <row r="120" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A120" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B120" s="8">
         <v>11419</v>
@@ -5375,7 +5356,7 @@
     </row>
     <row r="121" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A121" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B121" s="8">
         <v>8136</v>
@@ -5404,7 +5385,7 @@
     </row>
     <row r="122" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A122" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B122" s="8">
         <v>80243</v>
@@ -5433,7 +5414,7 @@
     </row>
     <row r="123" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A123" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B123" s="8">
         <v>5686</v>
@@ -5462,7 +5443,7 @@
     </row>
     <row r="124" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A124" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B124" s="8">
         <v>11368</v>
@@ -5491,7 +5472,7 @@
     </row>
     <row r="125" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A125" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B125" s="8">
         <v>4951</v>
@@ -5520,7 +5501,7 @@
     </row>
     <row r="126" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A126" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B126" s="8">
         <v>41631</v>
@@ -5549,7 +5530,7 @@
     </row>
     <row r="127" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A127" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B127" s="8">
         <v>33824</v>
@@ -5578,7 +5559,7 @@
     </row>
     <row r="128" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A128" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B128" s="8">
         <v>6798</v>
@@ -5607,7 +5588,7 @@
     </row>
     <row r="129" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A129" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B129" s="8">
         <v>10334</v>
@@ -5636,7 +5617,7 @@
     </row>
     <row r="130" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A130" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B130" s="8">
         <v>15737</v>
@@ -5665,7 +5646,7 @@
     </row>
     <row r="131" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B131" s="8">
         <v>111423</v>
@@ -5694,7 +5675,7 @@
     </row>
     <row r="132" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A132" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B132" s="8">
         <v>21395</v>
@@ -5723,7 +5704,7 @@
     </row>
     <row r="133" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A133" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B133" s="8">
         <v>11781</v>
@@ -5752,7 +5733,7 @@
     </row>
     <row r="134" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A134" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B134" s="8">
         <v>94449</v>
@@ -5781,7 +5762,7 @@
     </row>
     <row r="135" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A135" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B135" s="8">
         <v>13130</v>
@@ -5810,7 +5791,7 @@
     </row>
     <row r="136" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A136" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B136" s="8">
         <v>60746</v>
@@ -5839,7 +5820,7 @@
     </row>
     <row r="137" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A137" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B137" s="8">
         <v>5423</v>
@@ -5868,7 +5849,7 @@
     </row>
     <row r="138" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A138" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B138" s="8">
         <v>23987</v>
@@ -5897,7 +5878,7 @@
     </row>
     <row r="139" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A139" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B139" s="8">
         <v>20574</v>
@@ -5926,7 +5907,7 @@
     </row>
     <row r="140" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A140" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B140" s="8">
         <v>5132</v>
@@ -5955,7 +5936,7 @@
     </row>
     <row r="141" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A141" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B141" s="8">
         <v>39673</v>
@@ -5984,7 +5965,7 @@
     </row>
     <row r="142" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A142" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B142" s="8">
         <v>25794</v>
@@ -6013,7 +5994,7 @@
     </row>
     <row r="143" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A143" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B143" s="8">
         <v>14094</v>
@@ -6042,7 +6023,7 @@
     </row>
     <row r="144" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A144" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B144" s="8">
         <v>6372</v>
@@ -6071,7 +6052,7 @@
     </row>
     <row r="145" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A145" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B145" s="8">
         <v>10654</v>
@@ -6100,7 +6081,7 @@
     </row>
     <row r="146" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A146" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B146" s="8">
         <v>57484</v>
@@ -6129,7 +6110,7 @@
     </row>
     <row r="147" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A147" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B147" s="8">
         <v>13405</v>
@@ -6158,7 +6139,7 @@
     </row>
     <row r="148" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A148" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B148" s="8">
         <v>28120</v>
@@ -6187,7 +6168,7 @@
     </row>
     <row r="149" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A149" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B149" s="8">
         <v>6176</v>
@@ -6216,7 +6197,7 @@
     </row>
     <row r="150" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A150" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B150" s="8">
         <v>7001</v>
@@ -6245,7 +6226,7 @@
     </row>
     <row r="151" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A151" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B151" s="8">
         <v>50727</v>
@@ -6274,7 +6255,7 @@
     </row>
     <row r="152" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A152" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B152" s="8">
         <v>25183</v>
@@ -6303,7 +6284,7 @@
     </row>
     <row r="153" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A153" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B153" s="8">
         <v>10113</v>
@@ -6332,7 +6313,7 @@
     </row>
     <row r="154" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A154" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B154" s="8">
         <v>29015</v>
@@ -6361,7 +6342,7 @@
     </row>
     <row r="155" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A155" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B155" s="8">
         <v>13837</v>
@@ -6390,7 +6371,7 @@
     </row>
     <row r="156" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A156" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B156" s="8">
         <v>3249</v>
@@ -6419,7 +6400,7 @@
     </row>
     <row r="157" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A157" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B157" s="8">
         <v>27471</v>
@@ -6448,7 +6429,7 @@
     </row>
     <row r="158" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A158" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B158" s="8">
         <v>8851</v>
@@ -6477,7 +6458,7 @@
     </row>
     <row r="159" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A159" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B159" s="8">
         <v>8298</v>
@@ -6506,7 +6487,7 @@
     </row>
     <row r="160" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A160" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B160" s="8">
         <v>3511</v>
@@ -6535,7 +6516,7 @@
     </row>
     <row r="161" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A161" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B161" s="8">
         <v>11393</v>
@@ -6564,7 +6545,7 @@
     </row>
     <row r="162" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A162" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B162" s="8">
         <v>36358</v>
@@ -6593,7 +6574,7 @@
     </row>
     <row r="163" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A163" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B163" s="8">
         <v>31275</v>
@@ -6622,7 +6603,7 @@
     </row>
     <row r="164" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A164" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B164" s="8">
         <v>94613</v>
@@ -6651,7 +6632,7 @@
     </row>
     <row r="165" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A165" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B165" s="8">
         <v>1024</v>
@@ -6680,7 +6661,7 @@
     </row>
     <row r="166" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A166" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B166" s="8">
         <v>18158</v>
@@ -6709,7 +6690,7 @@
     </row>
     <row r="167" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A167" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B167" s="8">
         <v>88658</v>
@@ -6738,7 +6719,7 @@
     </row>
     <row r="168" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A168" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B168" s="8">
         <v>11992</v>
@@ -6767,7 +6748,7 @@
     </row>
     <row r="169" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A169" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B169" s="8">
         <v>12800</v>
@@ -6796,7 +6777,7 @@
     </row>
     <row r="170" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A170" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B170" s="8">
         <v>28735</v>
@@ -6825,7 +6806,7 @@
     </row>
     <row r="171" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A171" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B171" s="8">
         <v>31428</v>
@@ -6854,7 +6835,7 @@
     </row>
     <row r="172" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A172" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B172" s="8">
         <v>29202</v>
@@ -6883,7 +6864,7 @@
     </row>
     <row r="173" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A173" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B173" s="8">
         <v>15075</v>
@@ -6912,7 +6893,7 @@
     </row>
     <row r="174" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A174" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B174" s="8">
         <v>16732</v>
@@ -6941,7 +6922,7 @@
     </row>
     <row r="175" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A175" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B175" s="8">
         <v>2988</v>
@@ -6970,7 +6951,7 @@
     </row>
     <row r="176" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A176" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B176" s="8">
         <v>15687</v>
@@ -6999,7 +6980,7 @@
     </row>
     <row r="177" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A177" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B177" s="8">
         <v>19894</v>
@@ -7028,7 +7009,7 @@
     </row>
     <row r="178" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A178" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B178" s="8">
         <v>11105</v>
@@ -7057,7 +7038,7 @@
     </row>
     <row r="179" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A179" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B179" s="8">
         <v>29185</v>
@@ -7086,7 +7067,7 @@
     </row>
     <row r="180" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A180" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B180" s="8">
         <v>4681</v>
@@ -7115,7 +7096,7 @@
     </row>
     <row r="181" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A181" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B181" s="8">
         <v>1955</v>
@@ -7144,7 +7125,7 @@
     </row>
     <row r="182" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A182" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B182" s="8">
         <v>7643</v>
@@ -7173,7 +7154,7 @@
     </row>
     <row r="183" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A183" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B183" s="8">
         <v>5742</v>
@@ -7202,7 +7183,7 @@
     </row>
     <row r="184" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A184" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B184" s="8">
         <v>13973</v>
@@ -7231,7 +7212,7 @@
     </row>
     <row r="185" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A185" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B185" s="8">
         <v>12258</v>
@@ -7260,7 +7241,7 @@
     </row>
     <row r="186" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A186" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B186" s="8">
         <v>4944</v>
@@ -7289,7 +7270,7 @@
     </row>
     <row r="187" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A187" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B187" s="8">
         <v>53104</v>
@@ -7318,7 +7299,7 @@
     </row>
     <row r="188" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A188" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B188" s="8">
         <v>1322</v>
@@ -7347,7 +7328,7 @@
     </row>
     <row r="189" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A189" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B189" s="8">
         <v>18378</v>
@@ -7376,7 +7357,7 @@
     </row>
     <row r="190" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A190" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B190" s="8">
         <v>12146</v>
@@ -7405,7 +7386,7 @@
     </row>
     <row r="191" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A191" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B191" s="8">
         <v>42268</v>
@@ -7434,7 +7415,7 @@
     </row>
     <row r="192" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A192" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B192" s="8">
         <v>9281</v>
@@ -7463,7 +7444,7 @@
     </row>
     <row r="193" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A193" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B193" s="8">
         <v>60870</v>
@@ -7492,7 +7473,7 @@
     </row>
     <row r="194" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A194" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B194" s="8">
         <v>2980</v>
@@ -7521,7 +7502,7 @@
     </row>
     <row r="195" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A195" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B195" s="8">
         <v>3459</v>
@@ -7550,7 +7531,7 @@
     </row>
     <row r="196" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A196" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B196" s="8">
         <v>2939</v>
@@ -7579,7 +7560,7 @@
     </row>
     <row r="197" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A197" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B197" s="8">
         <v>94113</v>
@@ -7608,7 +7589,7 @@
     </row>
     <row r="198" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A198" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B198" s="8">
         <v>34385</v>
@@ -7637,7 +7618,7 @@
     </row>
     <row r="199" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A199" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B199" s="8">
         <v>14322</v>
@@ -7666,7 +7647,7 @@
     </row>
     <row r="200" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A200" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B200" s="8">
         <v>25305</v>
@@ -7695,7 +7676,7 @@
     </row>
     <row r="201" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A201" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B201" s="8">
         <v>12252</v>
@@ -7724,7 +7705,7 @@
     </row>
     <row r="202" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A202" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B202" s="8">
         <v>53654</v>
@@ -7753,7 +7734,7 @@
     </row>
     <row r="203" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A203" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B203" s="8">
         <v>17879</v>
@@ -7782,7 +7763,7 @@
     </row>
     <row r="204" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A204" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B204" s="8">
         <v>7280</v>
@@ -7811,7 +7792,7 @@
     </row>
     <row r="205" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A205" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B205" s="8">
         <v>6372</v>
@@ -7840,7 +7821,7 @@
     </row>
     <row r="206" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A206" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B206" s="8">
         <v>8888</v>
@@ -7869,7 +7850,7 @@
     </row>
     <row r="207" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A207" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B207" s="8">
         <v>43443</v>
@@ -7898,7 +7879,7 @@
     </row>
     <row r="208" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A208" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B208" s="8">
         <v>9575</v>
@@ -7927,7 +7908,7 @@
     </row>
     <row r="209" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A209" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B209" s="8">
         <v>20016</v>
@@ -7956,7 +7937,7 @@
     </row>
     <row r="210" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A210" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B210" s="8">
         <v>28378</v>
@@ -7985,7 +7966,7 @@
     </row>
     <row r="211" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A211" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B211" s="8">
         <v>18774</v>
@@ -8014,7 +7995,7 @@
     </row>
     <row r="212" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A212" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B212" s="8">
         <v>15841</v>
@@ -8043,7 +8024,7 @@
     </row>
     <row r="213" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A213" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B213" s="8">
         <v>18973</v>
@@ -8072,7 +8053,7 @@
     </row>
     <row r="214" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A214" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B214" s="8">
         <v>7633</v>
@@ -8101,7 +8082,7 @@
     </row>
     <row r="215" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A215" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B215" s="8">
         <v>37983</v>
@@ -8130,7 +8111,7 @@
     </row>
     <row r="216" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A216" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B216" s="8">
         <v>18036</v>
@@ -8159,7 +8140,7 @@
     </row>
     <row r="217" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A217" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B217" s="8">
         <v>81668</v>
@@ -8188,7 +8169,7 @@
     </row>
     <row r="218" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A218" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B218" s="8">
         <v>6247</v>
@@ -8217,7 +8198,7 @@
     </row>
     <row r="219" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A219" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B219" s="8">
         <v>10140</v>
@@ -8246,7 +8227,7 @@
     </row>
     <row r="220" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A220" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B220" s="8">
         <v>16826</v>
@@ -8275,7 +8256,7 @@
     </row>
     <row r="221" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A221" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B221" s="8">
         <v>17816</v>
@@ -8304,7 +8285,7 @@
     </row>
     <row r="222" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A222" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B222" s="8">
         <v>9772</v>
@@ -8333,7 +8314,7 @@
     </row>
     <row r="223" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A223" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B223" s="8">
         <v>11911</v>
@@ -8362,7 +8343,7 @@
     </row>
     <row r="224" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A224" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B224" s="8">
         <v>154306</v>
@@ -8391,7 +8372,7 @@
     </row>
     <row r="225" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A225" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B225" s="8">
         <v>8175</v>
@@ -8420,7 +8401,7 @@
     </row>
     <row r="226" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A226" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B226" s="8">
         <v>1898</v>
@@ -8449,7 +8430,7 @@
     </row>
     <row r="227" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A227" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B227" s="8">
         <v>22732</v>
@@ -8478,7 +8459,7 @@
     </row>
     <row r="228" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A228" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B228" s="8">
         <v>28961</v>
@@ -8507,7 +8488,7 @@
     </row>
     <row r="229" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A229" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B229" s="8">
         <v>7234</v>
@@ -8536,7 +8517,7 @@
     </row>
     <row r="230" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A230" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B230" s="8">
         <v>9611</v>
@@ -8565,7 +8546,7 @@
     </row>
     <row r="231" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A231" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B231" s="8">
         <v>19727</v>
@@ -8594,7 +8575,7 @@
     </row>
     <row r="232" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A232" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B232" s="8">
         <v>3656</v>
@@ -8623,7 +8604,7 @@
     </row>
     <row r="233" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A233" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B233" s="8">
         <v>9551</v>
@@ -8652,7 +8633,7 @@
     </row>
     <row r="234" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A234" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B234" s="8">
         <v>15296</v>
@@ -8681,7 +8662,7 @@
     </row>
     <row r="235" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A235" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B235" s="8">
         <v>16681</v>
@@ -8710,7 +8691,7 @@
     </row>
     <row r="236" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A236" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B236" s="8">
         <v>57028</v>
@@ -8739,7 +8720,7 @@
     </row>
     <row r="237" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A237" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B237" s="8">
         <v>8109</v>
@@ -8768,7 +8749,7 @@
     </row>
     <row r="238" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A238" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B238" s="8">
         <v>31424</v>
@@ -8797,7 +8778,7 @@
     </row>
     <row r="239" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A239" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B239" s="8">
         <v>4116</v>
@@ -8826,7 +8807,7 @@
     </row>
     <row r="240" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A240" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B240" s="8">
         <v>6644</v>
@@ -8855,7 +8836,7 @@
     </row>
     <row r="241" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A241" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B241" s="8">
         <v>9546</v>
@@ -8884,7 +8865,7 @@
     </row>
     <row r="242" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A242" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B242" s="8">
         <v>1984</v>
@@ -8913,7 +8894,7 @@
     </row>
     <row r="243" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A243" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B243" s="8">
         <v>12456</v>
@@ -8942,7 +8923,7 @@
     </row>
     <row r="244" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A244" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B244" s="8">
         <v>14066</v>
@@ -8971,7 +8952,7 @@
     </row>
     <row r="245" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A245" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B245" s="8">
         <v>27178</v>
@@ -9000,7 +8981,7 @@
     </row>
     <row r="246" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A246" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B246" s="8">
         <v>1894</v>
@@ -9029,7 +9010,7 @@
     </row>
     <row r="247" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A247" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B247" s="8">
         <v>25150</v>
@@ -9058,7 +9039,7 @@
     </row>
     <row r="248" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A248" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B248" s="8">
         <v>62737</v>
@@ -9087,7 +9068,7 @@
     </row>
     <row r="249" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A249" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B249" s="8">
         <v>9804</v>
@@ -9116,7 +9097,7 @@
     </row>
     <row r="250" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A250" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B250" s="8">
         <v>22592</v>
@@ -9145,7 +9126,7 @@
     </row>
     <row r="251" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A251" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B251" s="8">
         <v>36189</v>
@@ -9174,7 +9155,7 @@
     </row>
     <row r="252" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A252" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B252" s="8">
         <v>13891</v>
@@ -9203,7 +9184,7 @@
     </row>
     <row r="253" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A253" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B253" s="8">
         <v>16925</v>
@@ -9232,7 +9213,7 @@
     </row>
     <row r="254" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A254" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B254" s="8">
         <v>29651</v>
@@ -9261,7 +9242,7 @@
     </row>
     <row r="255" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A255" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B255" s="8">
         <v>2705</v>
@@ -9290,7 +9271,7 @@
     </row>
     <row r="256" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A256" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B256" s="8">
         <v>5295</v>
@@ -9319,7 +9300,7 @@
     </row>
     <row r="257" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A257" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B257" s="8">
         <v>19155</v>
@@ -9348,7 +9329,7 @@
     </row>
     <row r="258" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A258" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B258" s="8">
         <v>8216</v>
@@ -9377,7 +9358,7 @@
     </row>
     <row r="259" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A259" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B259" s="8">
         <v>7248</v>
@@ -9406,7 +9387,7 @@
     </row>
     <row r="260" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A260" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B260" s="8">
         <v>41507</v>
@@ -9435,7 +9416,7 @@
     </row>
     <row r="261" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A261" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B261" s="8">
         <v>24403</v>
@@ -9464,7 +9445,7 @@
     </row>
     <row r="262" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A262" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B262" s="8">
         <v>7902</v>
@@ -9493,7 +9474,7 @@
     </row>
     <row r="263" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A263" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B263" s="8">
         <v>12138</v>
@@ -9522,7 +9503,7 @@
     </row>
     <row r="264" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A264" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B264" s="8">
         <v>15920</v>
@@ -9551,7 +9532,7 @@
     </row>
     <row r="265" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A265" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B265" s="8">
         <v>28628</v>
@@ -9580,7 +9561,7 @@
     </row>
     <row r="266" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A266" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B266" s="8">
         <v>2911</v>
@@ -9609,7 +9590,7 @@
     </row>
     <row r="267" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A267" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B267" s="8">
         <v>16199</v>
@@ -9638,7 +9619,7 @@
     </row>
     <row r="268" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A268" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B268" s="8">
         <v>57776</v>
@@ -9667,7 +9648,7 @@
     </row>
     <row r="269" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A269" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B269" s="8">
         <v>1589</v>
@@ -9696,7 +9677,7 @@
     </row>
     <row r="270" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A270" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B270" s="8">
         <v>15134</v>
@@ -9725,7 +9706,7 @@
     </row>
     <row r="271" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A271" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B271" s="8">
         <v>14730</v>
@@ -9754,7 +9735,7 @@
     </row>
     <row r="272" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A272" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B272" s="8">
         <v>2489</v>
@@ -9783,7 +9764,7 @@
     </row>
     <row r="273" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A273" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B273" s="8">
         <v>8021</v>
@@ -9812,7 +9793,7 @@
     </row>
     <row r="274" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A274" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B274" s="8">
         <v>23915</v>
@@ -9841,7 +9822,7 @@
     </row>
     <row r="275" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A275" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B275" s="8">
         <v>10897</v>
@@ -9870,7 +9851,7 @@
     </row>
     <row r="276" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A276" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B276" s="8">
         <v>22850</v>
@@ -9899,7 +9880,7 @@
     </row>
     <row r="277" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A277" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B277" s="8">
         <v>18692</v>
@@ -9928,7 +9909,7 @@
     </row>
     <row r="278" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A278" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B278" s="8">
         <v>40251</v>
@@ -9957,7 +9938,7 @@
     </row>
     <row r="279" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A279" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B279" s="8">
         <v>184945</v>
@@ -9986,7 +9967,7 @@
     </row>
     <row r="280" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A280" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B280" s="8">
         <v>1191</v>
@@ -10015,7 +9996,7 @@
     </row>
     <row r="281" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A281" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B281" s="8">
         <v>11989</v>
@@ -10044,7 +10025,7 @@
     </row>
     <row r="282" spans="1:9" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A282" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B282" s="8">
         <v>23076</v>
